--- a/research_data/MORE_HD_master_confirmatory_240runs.xlsx
+++ b/research_data/MORE_HD_master_confirmatory_240runs.xlsx
@@ -26240,7 +26240,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G402"/>
+  <dimension ref="A1:G404"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -40420,6 +40420,80 @@
         </is>
       </c>
     </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>18_Circuit_Benchmark</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>batch_size</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>per_block_model</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>benchmarks/circuit_microbenchmark_block&lt;k&gt;.json</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>rows[].batch_size</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>2026-10-04: satu repeat = satu forward pass batch ini (termasuk satu konstruksi U(theta)); waktu wall/cpu = per sampel</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>18_Circuit_Benchmark</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>unitary_median_sec</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>per_block_model</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>benchmarks/circuit_microbenchmark_block&lt;k&gt;.json</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>rows[].unitary_median_sec</t>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>Median waktu membangun kolom U(theta) sekali per objective evaluation</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A3:G397"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -40432,7 +40506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U3"/>
+  <dimension ref="A1:W3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -40569,6 +40643,16 @@
       <c r="U3" s="2" t="inlineStr">
         <is>
           <t>timestamp</t>
+        </is>
+      </c>
+      <c r="V3" s="3" t="inlineStr">
+        <is>
+          <t>batch_size</t>
+        </is>
+      </c>
+      <c r="W3" s="3" t="inlineStr">
+        <is>
+          <t>unitary_median_sec</t>
         </is>
       </c>
     </row>
